--- a/public/talent-card-template-en.xlsx
+++ b/public/talent-card-template-en.xlsx
@@ -26,16 +26,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <sz val="11"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3A6B"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,7 +57,9 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,41 +428,44 @@
   <dimension ref="A1:AI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="28" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="28" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
-    <col width="28" customWidth="1" min="20" max="20"/>
-    <col width="28" customWidth="1" min="21" max="21"/>
-    <col width="28" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="28" customWidth="1" min="24" max="24"/>
-    <col width="28" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="28" customWidth="1" min="27" max="27"/>
-    <col width="28" customWidth="1" min="28" max="28"/>
-    <col width="28" customWidth="1" min="29" max="29"/>
-    <col width="28" customWidth="1" min="30" max="30"/>
-    <col width="28" customWidth="1" min="31" max="31"/>
-    <col width="28" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="22" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="34" max="34"/>
+    <col width="22" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="45" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
@@ -478,12 +488,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Country of origin</t>
+          <t>Home Country</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Expatriation end date</t>
+          <t>End of expatriation</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -548,22 +558,22 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Next Target Position - Immediate</t>
+          <t>Targeted Next Role - Immediate</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Next Target Position - Short Term</t>
+          <t>Targeted Next Role - Short Term</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Next Target Position - Medium Term</t>
+          <t>Targeted Next Role - Medium Term</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Next Target Position - Long Term</t>
+          <t>Targeted Next Role - Long Term</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
@@ -633,145 +643,142 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>José da Silva</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Não</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Brazil</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr"/>
-      <c r="G2" s="1" t="inlineStr"/>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>NATIONAL EXPRESS MANAGER</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Marco Alcolezi</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2 years</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>21 years</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Key Players</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Top Talents</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Gas Stations and Drugstores</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Sam's Club Operations Director</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Audit Superintendent</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr"/>
-      <c r="W2" s="1" t="inlineStr"/>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr"/>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr"/>
-      <c r="AC2" s="1" t="inlineStr"/>
-      <c r="AD2" s="1" t="inlineStr"/>
-      <c r="AE2" s="1" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Carrefour Brazil;2019 to present: Operations Director;2016 to 2019: Regional Operations Manager;2012 to 2016: General Manager</t>
         </is>
       </c>
-      <c r="AF2" s="1" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>MBA in Physical and Online Retail - USP;Postgraduate in Organizational Development - FDC;Bachelor in Marketing - Anhanguera</t>
         </is>
       </c>
-      <c r="AG2" s="1" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Invests in self-development and career;Strong business and strategic vision;Works very well in teams</t>
         </is>
       </c>
-      <c r="AH2" s="1" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>Needs to develop talent in the team and build successors</t>
         </is>
       </c>
-      <c r="AI2" s="1" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>Scope expansion</t>
         </is>
@@ -779,19 +786,19 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="J2:J500 K2:K500 Z2:Z500 AA2:AA500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid selection" error="Select a value from the list." type="list" errorStyle="stop">
+    <dataValidation sqref="J2:J500 K2:K500 Z2:Z500 AA2:AA500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O500 P2:P500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid selection" error="Select a value from the list." type="list" errorStyle="stop">
+    <dataValidation sqref="O2:O500 P2:P500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Under Watching,Moderate Contributors,Top Talents,Key Players,Strong Professionals"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q500 R2:R500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid selection" error="Select a value from the list." type="list" errorStyle="stop">
+    <dataValidation sqref="Q2:Q500 R2:R500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="AI2:AI500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid selection" error="Select a value from the list." type="list" errorStyle="stop">
+    <dataValidation sqref="AI2:AI500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Strategic / cross-functional project,Expatriation,Scope expansion,Job Rotation,Mentoring / Coaching,Leadership or technical development,Others: describe"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Selecione Sim ou Não." type="list" errorStyle="stop">
+    <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/talent-card-template-en.xlsx
+++ b/public/talent-card-template-en.xlsx
@@ -638,7 +638,7 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Readiness (list)</t>
+          <t>Action Plan (list)</t>
         </is>
       </c>
     </row>

--- a/public/talent-card-template-en.xlsx
+++ b/public/talent-card-template-en.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
@@ -463,6 +463,7 @@
     <col width="22" customWidth="1" min="33" max="33"/>
     <col width="22" customWidth="1" min="34" max="34"/>
     <col width="22" customWidth="1" min="35" max="35"/>
+    <col width="22" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
@@ -513,130 +514,135 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Talent Factory (Y/N)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>C200 (Y/N)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Manager</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Time in Role</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Time in Company</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Box 2025 (list)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Box 2026 (list)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Risk of Loss (High/Medium/Low)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Position Criticality (High/Medium/Low)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Targeted Next Role - Immediate</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Targeted Next Role - Short Term</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Targeted Next Role - Medium Term</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Targeted Next Role - Long Term</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Language - Advanced</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Language - Intermediate</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Language - Basic</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>National Mobility (Y/N)</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>International Mobility (Y/N)</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Successors - Short Term (0–12 months)</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Successors - Medium Term (1–3 years)</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Successors - Long Term (3–5 years)</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Career History (separated by ;)</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Education (separated by ;)</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Competencies (separated by ;)</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Development Opportunities (separated by ;)</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Action Plan (list)</t>
         </is>
@@ -685,122 +691,130 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Marco Alcolezi</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2 years</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>21 years</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Key Players</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Top Talents</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Gas Stations and Drugstores</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Sam's Club Operations Director</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Audit Superintendent</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Carrefour Brazil;2019 to present: Operations Director;2016 to 2019: Regional Operations Manager;2012 to 2016: General Manager</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>MBA in Physical and Online Retail - USP;Postgraduate in Organizational Development - FDC;Bachelor in Marketing - Anhanguera</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>Invests in self-development and career;Strong business and strategic vision;Works very well in teams</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>Needs to develop talent in the team and build successors</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>Scope expansion</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation sqref="J2:J500 K2:K500 Z2:Z500 AA2:AA500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="6">
+    <dataValidation sqref="K2:K500 L2:L500 AA2:AA500 AB2:AB500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O500 P2:P500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P500 Q2:Q500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Under Watching,Moderate Contributors,Top Talents,Key Players,Strong Professionals"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q500 R2:R500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="R2:R500 S2:S500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="AI2:AI500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AJ2:AJ500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Strategic / cross-functional project,Expatriation,Scope expansion,Job Rotation,Mentoring / Coaching,Leadership or technical development,Others: describe"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
+    <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"SD,D,M"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/talent-card-template-en.xlsx
+++ b/public/talent-card-template-en.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ2"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -464,6 +464,7 @@
     <col width="22" customWidth="1" min="34" max="34"/>
     <col width="22" customWidth="1" min="35" max="35"/>
     <col width="22" customWidth="1" min="36" max="36"/>
+    <col width="22" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
@@ -544,105 +545,110 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>ID Criteria</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Box 2025 (list)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Box 2026 (list)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Risk of Loss (High/Medium/Low)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Position Criticality (High/Medium/Low)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Targeted Next Role - Immediate</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Targeted Next Role - Short Term</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Targeted Next Role - Medium Term</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Targeted Next Role - Long Term</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Language - Advanced</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Language - Intermediate</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Language - Basic</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>National Mobility (Y/N)</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>International Mobility (Y/N)</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Successors - Short Term (0–12 months)</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Successors - Medium Term (1–3 years)</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Successors - Long Term (3–5 years)</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Career History (separated by ;)</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Education (separated by ;)</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Competencies (separated by ;)</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Development Opportunities (separated by ;)</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Action Plan (list)</t>
         </is>
@@ -721,92 +727,97 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>Succ Plan</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Key Players</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>Top Talents</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Gas Stations and Drugstores</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Sam's Club Operations Director</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Audit Superintendent</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>English</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>Carrefour Brazil;2019 to present: Operations Director;2016 to 2019: Regional Operations Manager;2012 to 2016: General Manager</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>MBA in Physical and Online Retail - USP;Postgraduate in Organizational Development - FDC;Bachelor in Marketing - Anhanguera</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>Invests in self-development and career;Strong business and strategic vision;Works very well in teams</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>Needs to develop talent in the team and build successors</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>Scope expansion</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation sqref="K2:K500 L2:L500 AA2:AA500 AB2:AB500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="7">
+    <dataValidation sqref="K2:K500 L2:L500 AB2:AB500 AC2:AC500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P500 Q2:Q500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q500 R2:R500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Under Watching,Moderate Contributors,Top Talents,Key Players,Strong Professionals"</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R500 S2:S500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="S2:S500 T2:T500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
-    <dataValidation sqref="AJ2:AJ500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AK2:AK500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Strategic / cross-functional project,Expatriation,Scope expansion,Job Rotation,Mentoring / Coaching,Leadership or technical development,Others: describe"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -815,6 +826,9 @@
     <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SD,D,M"</formula1>
     </dataValidation>
+    <dataValidation sqref="P2:P500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"TT N-1 Comex,Succ Plan,Expatriate,Other"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
